--- a/01_Input/00_CO Validation/Turkey - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Turkey - Energy Projects.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27016"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ben/Documents/UNDP/Energy/CO Validation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="268" documentId="13_ncr:1_{0EFF3E03-FAB0-5547-AB89-E48C983D93AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{434C0190-9B7C-40D5-BABF-14F95CF72F79}"/>
+  <xr:revisionPtr revIDLastSave="272" documentId="13_ncr:1_{0EFF3E03-FAB0-5547-AB89-E48C983D93AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7BE7B853-1C24-420E-9AAF-2BF61BBE685C}"/>
   <bookViews>
     <workbookView xWindow="7500" yWindow="740" windowWidth="16100" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,6 +20,9 @@
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="104">
   <si>
     <t>Project ID</t>
   </si>
@@ -147,7 +150,7 @@
     <t>http://open.undp.org/projects/00125243</t>
   </si>
   <si>
-    <t>Capacity Training</t>
+    <t>Entrepreneurship Training</t>
   </si>
   <si>
     <t>Number of trainees trained at the vocational training center(s) supported(at least 25 % are women)</t>
@@ -226,7 +229,7 @@
     <t>PIMS+</t>
   </si>
   <si>
-    <t>Other Energy Services</t>
+    <t>GHG Emissions Reduction</t>
   </si>
   <si>
     <t>tCO2</t>
@@ -361,6 +364,12 @@
     <t>to the CO: Please estimate number of beneficiaries.</t>
   </si>
   <si>
+    <t>Capacity Training</t>
+  </si>
+  <si>
+    <t>Other Energy Services</t>
+  </si>
+  <si>
     <t># of pilot projects at farm and enterprise levels on resource efficiency in agriculture and agro-industries</t>
   </si>
   <si>
@@ -471,9 +480,6 @@
   </si>
   <si>
     <t>Individuals who participate in trainings for energy activities</t>
-  </si>
-  <si>
-    <t>Entrepreneurship Training</t>
   </si>
   <si>
     <t>Training for enterprises on the energy business is assumed to result in at least 100 direct beneficiaries</t>
@@ -676,18 +682,6 @@
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -714,6 +708,18 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1042,401 +1048,401 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="30.75">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="C1" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="E1" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="16" t="s">
+      <c r="F1" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="16" t="s">
+      <c r="G1" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="16" t="s">
+      <c r="H1" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="16" t="s">
+      <c r="I1" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="16" t="s">
+      <c r="J1" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="17" t="s">
+      <c r="K1" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="17" t="s">
+      <c r="L1" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="17" t="s">
+      <c r="M1" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="17" t="s">
+      <c r="N1" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="17" t="s">
+      <c r="O1" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="17" t="s">
+      <c r="P1" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="17" t="s">
+      <c r="Q1" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="17" t="s">
+      <c r="R1" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="17" t="s">
+      <c r="S1" s="13" t="s">
         <v>18</v>
       </c>
       <c r="T1" s="7"/>
     </row>
     <row r="2" spans="1:20" ht="91.5">
-      <c r="A2" s="18">
+      <c r="A2" s="14">
         <v>96620</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="19" t="s">
+      <c r="C2" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="18">
+      <c r="D2" s="14">
         <v>1499060</v>
       </c>
-      <c r="E2" s="20" t="s">
+      <c r="E2" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="F2" s="20" t="s">
+      <c r="F2" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="G2" s="20">
+      <c r="G2" s="16">
         <v>0</v>
       </c>
-      <c r="H2" s="20">
+      <c r="H2" s="16">
         <v>300</v>
       </c>
-      <c r="I2" s="20" t="s">
+      <c r="I2" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="J2" s="20" t="s">
+      <c r="J2" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="K2" s="21"/>
-      <c r="L2" s="18" t="s">
+      <c r="K2" s="17"/>
+      <c r="L2" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="M2" s="18"/>
-      <c r="N2" s="18"/>
-      <c r="O2" s="18" t="s">
+      <c r="M2" s="14"/>
+      <c r="N2" s="14"/>
+      <c r="O2" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="P2" s="18" t="s">
+      <c r="P2" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="Q2" s="18"/>
-      <c r="R2" s="18"/>
-      <c r="S2" s="18"/>
+      <c r="Q2" s="14"/>
+      <c r="R2" s="14"/>
+      <c r="S2" s="14"/>
     </row>
     <row r="3" spans="1:20" ht="180.75" customHeight="1">
-      <c r="A3" s="18">
+      <c r="A3" s="14">
         <v>114367</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="D3" s="18">
+      <c r="D3" s="14">
         <v>791900</v>
       </c>
-      <c r="E3" s="20" t="s">
+      <c r="E3" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="F3" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="G3" s="20"/>
-      <c r="H3" s="20"/>
-      <c r="I3" s="20" t="s">
+      <c r="G3" s="16"/>
+      <c r="H3" s="16"/>
+      <c r="I3" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="J3" s="20" t="s">
+      <c r="J3" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="K3" s="18"/>
-      <c r="L3" s="18" t="s">
+      <c r="K3" s="14"/>
+      <c r="L3" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="M3" s="18"/>
-      <c r="N3" s="18"/>
-      <c r="O3" s="18" t="s">
+      <c r="M3" s="14"/>
+      <c r="N3" s="14"/>
+      <c r="O3" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="P3" s="18" t="s">
+      <c r="P3" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="Q3" s="18"/>
-      <c r="R3" s="18" t="s">
+      <c r="Q3" s="14"/>
+      <c r="R3" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="S3" s="18" t="s">
+      <c r="S3" s="14" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:20" ht="212.25" customHeight="1">
-      <c r="A4" s="18">
+      <c r="A4" s="14">
         <v>125243</v>
       </c>
-      <c r="B4" s="18" t="s">
+      <c r="B4" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="D4" s="18">
+      <c r="D4" s="14">
         <v>2362663</v>
       </c>
-      <c r="E4" s="20" t="s">
+      <c r="E4" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="F4" s="20" t="s">
+      <c r="F4" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="G4" s="20">
+      <c r="G4" s="16">
         <v>0</v>
       </c>
-      <c r="H4" s="20">
+      <c r="H4" s="16">
         <v>1600</v>
       </c>
-      <c r="I4" s="22" t="s">
+      <c r="I4" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="J4" s="20" t="s">
+      <c r="J4" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="K4" s="23">
+      <c r="K4" s="19">
         <v>0.25</v>
       </c>
-      <c r="L4" s="18" t="s">
+      <c r="L4" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="M4" s="18"/>
-      <c r="N4" s="18"/>
-      <c r="O4" s="18" t="s">
+      <c r="M4" s="14"/>
+      <c r="N4" s="14"/>
+      <c r="O4" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="P4" s="18" t="s">
+      <c r="P4" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="Q4" s="18"/>
-      <c r="R4" s="18"/>
-      <c r="S4" s="18"/>
+      <c r="Q4" s="14"/>
+      <c r="R4" s="14"/>
+      <c r="S4" s="14"/>
     </row>
     <row r="5" spans="1:20" ht="130.5" customHeight="1">
-      <c r="A5" s="18">
+      <c r="A5" s="14">
         <v>133485</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="D5" s="18">
+      <c r="D5" s="14">
         <v>170000</v>
       </c>
-      <c r="E5" s="20" t="s">
+      <c r="E5" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="F5" s="20" t="s">
+      <c r="F5" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="G5" s="20" t="s">
+      <c r="G5" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="H5" s="20"/>
-      <c r="I5" s="20" t="s">
+      <c r="H5" s="16"/>
+      <c r="I5" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="J5" s="20" t="s">
+      <c r="J5" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="K5" s="23">
+      <c r="K5" s="19">
         <v>0.5</v>
       </c>
-      <c r="L5" s="18" t="s">
+      <c r="L5" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="M5" s="18"/>
-      <c r="N5" s="18"/>
-      <c r="O5" s="18" t="s">
+      <c r="M5" s="14"/>
+      <c r="N5" s="14"/>
+      <c r="O5" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="P5" s="18" t="s">
+      <c r="P5" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="Q5" s="18"/>
-      <c r="R5" s="18" t="s">
+      <c r="Q5" s="14"/>
+      <c r="R5" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="S5" s="18" t="s">
+      <c r="S5" s="14" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:20" ht="211.5" customHeight="1">
-      <c r="A6" s="18">
+      <c r="A6" s="14">
         <v>5673</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="D6" s="18">
+      <c r="D6" s="14">
         <v>3800000</v>
       </c>
-      <c r="E6" s="20" t="s">
+      <c r="E6" t="s">
         <v>51</v>
       </c>
-      <c r="F6" s="20" t="s">
+      <c r="F6" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="G6" s="20">
+      <c r="G6" s="16">
         <v>0</v>
       </c>
-      <c r="H6" s="20">
+      <c r="H6" s="16">
         <v>311205</v>
       </c>
-      <c r="I6" s="22" t="s">
+      <c r="I6" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="J6" s="20" t="s">
+      <c r="J6" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="K6" s="18"/>
-      <c r="L6" s="18" t="s">
+      <c r="K6" s="14"/>
+      <c r="L6" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="M6" s="18"/>
-      <c r="N6" s="18"/>
-      <c r="O6" s="18" t="s">
+      <c r="M6" s="14"/>
+      <c r="N6" s="14"/>
+      <c r="O6" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="P6" s="18" t="s">
+      <c r="P6" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="Q6" s="18"/>
-      <c r="R6" s="18"/>
-      <c r="S6" s="18"/>
+      <c r="Q6" s="14"/>
+      <c r="R6" s="14"/>
+      <c r="S6" s="14"/>
     </row>
     <row r="7" spans="1:20" ht="178.5" customHeight="1">
-      <c r="A7" s="18">
+      <c r="A7" s="14">
         <v>5323</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="C7" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="D7" s="18">
+      <c r="D7" s="14">
         <v>3780000</v>
       </c>
-      <c r="E7" s="20" t="s">
+      <c r="E7" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="F7" s="20" t="s">
+      <c r="F7" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="G7" s="20">
+      <c r="G7" s="16">
         <v>0</v>
       </c>
-      <c r="H7" s="20">
+      <c r="H7" s="16">
         <v>3487</v>
       </c>
-      <c r="I7" s="22" t="s">
+      <c r="I7" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="J7" s="20" t="s">
+      <c r="J7" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="K7" s="18"/>
-      <c r="L7" s="18" t="s">
+      <c r="K7" s="14"/>
+      <c r="L7" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="M7" s="18"/>
-      <c r="N7" s="18"/>
-      <c r="O7" s="18" t="s">
+      <c r="M7" s="14"/>
+      <c r="N7" s="14"/>
+      <c r="O7" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="P7" s="18" t="s">
+      <c r="P7" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="Q7" s="18"/>
-      <c r="R7" s="18"/>
-      <c r="S7" s="18"/>
+      <c r="Q7" s="14"/>
+      <c r="R7" s="14"/>
+      <c r="S7" s="14"/>
     </row>
     <row r="8" spans="1:20" ht="192" customHeight="1">
-      <c r="A8" s="18">
+      <c r="A8" s="14">
         <v>5285</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="C8" s="18" t="s">
+      <c r="C8" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="D8" s="18">
+      <c r="D8" s="14">
         <v>3750000</v>
       </c>
-      <c r="E8" s="20" t="s">
+      <c r="E8" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="F8" s="20" t="s">
+      <c r="F8" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="G8" s="20">
+      <c r="G8" s="16">
         <v>0</v>
       </c>
-      <c r="H8" s="20">
+      <c r="H8" s="16">
         <v>5000</v>
       </c>
-      <c r="I8" s="22" t="s">
+      <c r="I8" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="J8" s="20" t="s">
+      <c r="J8" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="K8" s="18"/>
-      <c r="L8" s="18" t="s">
+      <c r="K8" s="14"/>
+      <c r="L8" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="M8" s="24" t="s">
+      <c r="M8" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="N8" s="18"/>
-      <c r="O8" s="18" t="s">
+      <c r="N8" s="14"/>
+      <c r="O8" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="P8" s="18" t="s">
+      <c r="P8" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="Q8" s="18"/>
-      <c r="R8" s="18"/>
-      <c r="S8" s="18"/>
+      <c r="Q8" s="14"/>
+      <c r="R8" s="14"/>
+      <c r="S8" s="14"/>
     </row>
   </sheetData>
   <dataValidations count="5">
@@ -1653,7 +1659,7 @@
         <v>2362663</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="F4" s="6" t="s">
         <v>37</v>
@@ -1745,7 +1751,7 @@
         <v>3800000</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>52</v>
@@ -1965,7 +1971,7 @@
         <v>21</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G2" s="3">
         <v>0</v>
@@ -1980,7 +1986,7 @@
         <v>23</v>
       </c>
       <c r="K2" s="8" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="231" customHeight="1">
@@ -2003,10 +2009,10 @@
         <v>30</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I3" s="6" t="s">
         <v>31</v>
@@ -2029,7 +2035,7 @@
         <v>2362663</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="F4" s="6" t="s">
         <v>37</v>
@@ -2061,7 +2067,7 @@
         <v>170000</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>43</v>
@@ -2070,7 +2076,7 @@
         <v>44</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I5" s="6" t="s">
         <v>45</v>
@@ -2093,10 +2099,10 @@
         <v>3800000</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G6" s="6">
         <v>0</v>
@@ -2128,7 +2134,7 @@
         <v>57</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G7" s="3">
         <v>0</v>
@@ -2208,160 +2214,160 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="12" t="s">
-        <v>73</v>
+      <c r="A2" s="21" t="s">
+        <v>75</v>
       </c>
       <c r="B2" t="s">
         <v>57</v>
       </c>
       <c r="C2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="12"/>
+      <c r="A3" s="21"/>
       <c r="B3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="12"/>
+      <c r="A4" s="21"/>
       <c r="B4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C4" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="13" t="s">
-        <v>79</v>
+      <c r="A5" s="22" t="s">
+        <v>81</v>
       </c>
       <c r="B5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C5" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="13"/>
+      <c r="A6" s="22"/>
       <c r="B6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="13"/>
+      <c r="A7" s="22"/>
       <c r="B7" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C7" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="13"/>
+      <c r="A8" s="22"/>
       <c r="B8" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C8" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="13"/>
+      <c r="A9" s="22"/>
       <c r="B9" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="C9" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="14" t="s">
-        <v>89</v>
+      <c r="A10" s="23" t="s">
+        <v>91</v>
       </c>
       <c r="B10" t="s">
         <v>21</v>
       </c>
       <c r="C10" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="14"/>
+      <c r="A11" s="23"/>
       <c r="B11" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C11" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="15" t="s">
-        <v>93</v>
+      <c r="A12" s="24" t="s">
+        <v>95</v>
       </c>
       <c r="B12" t="s">
+        <v>64</v>
+      </c>
+      <c r="C12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="24"/>
+      <c r="B13" t="s">
         <v>36</v>
       </c>
-      <c r="C12" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="15"/>
-      <c r="B13" t="s">
-        <v>95</v>
-      </c>
       <c r="C13" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="15"/>
+      <c r="A14" s="24"/>
       <c r="B14" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C14" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B15" t="s">
         <v>29</v>
       </c>
       <c r="C15" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B16" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C16" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>
@@ -2376,17 +2382,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0d2b1cfbe0bead55dc04bff20486709a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a3ed273af6605fa6a207dd3965c2d078" ns2:_="" ns3:_="">
     <xsd:import namespace="720239d0-7d3a-4257-bb40-a2a3b1409bb2"/>
@@ -2635,6 +2630,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -2645,11 +2651,11 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D95151FA-9580-4149-A82E-5CCA90355502}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B2021D64-63CF-41B0-AAED-0CD8BAFB5D20}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B2021D64-63CF-41B0-AAED-0CD8BAFB5D20}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D95151FA-9580-4149-A82E-5CCA90355502}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>

--- a/01_Input/00_CO Validation/Turkey - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Turkey - Energy Projects.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27016"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27226"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ben/Documents/UNDP/Energy/CO Validation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="272" documentId="13_ncr:1_{0EFF3E03-FAB0-5547-AB89-E48C983D93AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7BE7B853-1C24-420E-9AAF-2BF61BBE685C}"/>
+  <xr:revisionPtr revIDLastSave="305" documentId="13_ncr:1_{0EFF3E03-FAB0-5547-AB89-E48C983D93AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DAA81A35-2EC1-4946-BF43-BA369B9FE81B}"/>
   <bookViews>
     <workbookView xWindow="7500" yWindow="740" windowWidth="16100" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="117">
   <si>
     <t>Project ID</t>
   </si>
@@ -74,10 +74,7 @@
     <t>Gender (% female)</t>
   </si>
   <si>
-    <t>Category</t>
-  </si>
-  <si>
-    <t>Comments</t>
+    <t>VF or Non-VF</t>
   </si>
   <si>
     <t>Tag</t>
@@ -96,6 +93,15 @@
   </si>
   <si>
     <t>Indirect Taxonomy</t>
+  </si>
+  <si>
+    <t>Technology</t>
+  </si>
+  <si>
+    <t>Policy or Regulatory Framework</t>
+  </si>
+  <si>
+    <t>Policy Population</t>
   </si>
   <si>
     <t>Resource Efficiency in Agriculture &amp; Agrobased Ind.GAP</t>
@@ -129,9 +135,6 @@
     <t>http://open.undp.org/projects/00114367</t>
   </si>
   <si>
-    <t>Policy or Regulatory Framework</t>
-  </si>
-  <si>
     <t>Mapping of legislative requirements in place</t>
   </si>
   <si>
@@ -142,6 +145,12 @@
   </si>
   <si>
     <t>Legal Framework</t>
+  </si>
+  <si>
+    <t>National</t>
+  </si>
+  <si>
+    <t>Tier 1</t>
   </si>
   <si>
     <t>Increasing Employability in the Renewable Energy Sector</t>
@@ -205,6 +214,9 @@
     <t>http://open.undp.org/projects/00133485</t>
   </si>
   <si>
+    <t>Small Enterprises</t>
+  </si>
+  <si>
     <t>Number of tourism actors that integrated at least one energy efficiency application and/or use of renewable energy resources.</t>
   </si>
   <si>
@@ -215,6 +227,9 @@
   </si>
   <si>
     <t>Enerjisa</t>
+  </si>
+  <si>
+    <t>Tier 2</t>
   </si>
   <si>
     <t>Incentives and Support</t>
@@ -320,6 +335,9 @@
     </r>
   </si>
   <si>
+    <t>Solar</t>
+  </si>
+  <si>
     <t>TEEEM - EE Motors</t>
   </si>
   <si>
@@ -364,6 +382,12 @@
     <t>to the CO: Please estimate number of beneficiaries.</t>
   </si>
   <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Comments</t>
+  </si>
+  <si>
     <t>Capacity Training</t>
   </si>
   <si>
@@ -410,91 +434,106 @@
     <t>Cumulative installed capacity of grid-connected PV systems (kWp)</t>
   </si>
   <si>
-    <t>Tier</t>
-  </si>
-  <si>
-    <t>Explanation</t>
-  </si>
-  <si>
-    <t>Access to Energy</t>
-  </si>
-  <si>
-    <t>Access to electricity (direct access to electricity, lighting,  heating, cooling etc.)</t>
+    <t>Number of people, disaggregated by sex, who gain access to clean electricity (direct access to electricity, lighting, cooling, etc.) </t>
   </si>
   <si>
     <t>Energy (MW added)</t>
   </si>
   <si>
-    <t>Access to energy through installed renewable energy capacity (solar PV, hydro, wind, etc. )</t>
+    <t>Number of MW installed capacity</t>
   </si>
   <si>
     <t>Clean Cooking</t>
   </si>
   <si>
-    <t>Access to clean cooking (direct access to clean cook stoves, clean fuels, biomass, etc.)</t>
-  </si>
-  <si>
-    <t>Productive Use of Energy</t>
-  </si>
-  <si>
-    <t>Agricultural Services</t>
-  </si>
-  <si>
-    <t>Access to agricultural energy services (irrigation with solar pumps, heating systems for processing food, etc. )</t>
+    <t>Number of people who gain access to clean cooking (direct access to clean cook stoves, clean fuels, biomass, etc.).</t>
+  </si>
+  <si>
+    <t>Clean Heating</t>
+  </si>
+  <si>
+    <t>Number of people who gain access to clean heating (direct access to clean electric heaters, clean fuels, etc.).</t>
+  </si>
+  <si>
+    <t>Agriculture and Food System</t>
+  </si>
+  <si>
+    <t>Number of people who gain access to clean, affordable, and sustainable electricity for agricultural and food system activities (direct access to power machines for crop, processing, milling, grinding, de-husking, pressing, canning, sealing and packaging electricity, heating, cooling, solar water pumping for irrigation etc.) </t>
   </si>
   <si>
     <t>Health Services</t>
   </si>
   <si>
-    <t>Access to health services powered by solar PV and energy efficient systems such as hospitals</t>
+    <t>Number of people who gain access to health care facilities (direct access to electricity and heating systems for clinics, hospitals, health centers etc.) </t>
   </si>
   <si>
     <t>Water Services</t>
   </si>
   <si>
-    <t>Access to solar water pumps</t>
+    <t>Number of people who gain access to water services (powering water pumps, water distributions, waste management, etc.).  </t>
   </si>
   <si>
     <t>Education Services</t>
   </si>
   <si>
-    <t>Access to education services trough clean energy systems</t>
+    <t>Number of people who gain access to education services through clean energy systems (including students, teachers, etc.) </t>
+  </si>
+  <si>
+    <t>Transportation and E-mobility Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of MJ saved from transport and e-mobility interventions (e.g., electric vehicles, charging stations, etc.)  </t>
+  </si>
+  <si>
+    <t>Energy Efficiency Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of MJ saved from energy efficiency interventions (e.g., building efficiency, industries, etc.)  </t>
+  </si>
+  <si>
+    <t>Energy Infrastructure Services</t>
+  </si>
+  <si>
+    <t>Number of people who benefits from energy infrastructure interventions (streetlight, transmission, and distribution lines, etc.) </t>
   </si>
   <si>
     <t>Access to other service (electric vehicles, industries efficiency etc.)</t>
   </si>
   <si>
-    <t>Market Development</t>
+    <t xml:space="preserve">Financing support </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support for the development of market ecosystem </t>
   </si>
   <si>
     <t>Support for the development of medium enterprises in the energy transition market</t>
   </si>
   <si>
-    <t>Small Enterprises</t>
-  </si>
-  <si>
     <t>Support for the development of small enterprises in the energy transition market</t>
   </si>
   <si>
-    <t>Capacity Building</t>
-  </si>
-  <si>
-    <t>Individuals who participate in trainings for energy activities</t>
+    <t>Capacity Building Training</t>
+  </si>
+  <si>
+    <t>Number of people who benefits from training for enterprises on the energy business and energy finance. </t>
   </si>
   <si>
     <t>Training for enterprises on the energy business is assumed to result in at least 100 direct beneficiaries</t>
   </si>
   <si>
+    <t>Market Intervention</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Volume of investment (US dollars) leverage removing barriers to private and public investment in clean, reliable, affordable, and sustainable energy solutions and energy efficiency for social infrastructure, productive use of electricity and other services </t>
+  </si>
+  <si>
     <t>Campaign Participant</t>
   </si>
   <si>
     <t>Individuals who participate in advocacy and campaign on energy</t>
   </si>
   <si>
-    <t>Policy and Regulator Frameworks</t>
-  </si>
-  <si>
-    <t>Policies and regulatory framework can have far-reaching impacts on the energy access situation in countries</t>
+    <t xml:space="preserve">Number of people supported by policy and regulatory framework development on clean, affordable, and sustainable energy </t>
   </si>
   <si>
     <t>Other</t>
@@ -507,12 +546,18 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -560,8 +605,21 @@
       <name val="Helvetica Neue"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -574,44 +632,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAFFFFD"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7FFFFB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF42FFFA"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00E1DA"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00DAD3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00BDB7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="3">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -649,77 +671,146 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1026,7 +1117,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC7FC47B-9AC6-462B-BC07-1DA627AEFE8D}">
-  <dimension ref="A1:T8"/>
+  <dimension ref="A1:AF8"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="49" customWidth="1"/>
@@ -1039,427 +1130,578 @@
     <col min="9" max="9" width="59.28515625" customWidth="1"/>
     <col min="10" max="10" width="11.7109375" customWidth="1"/>
     <col min="11" max="11" width="18.28515625" customWidth="1"/>
-    <col min="12" max="12" width="9.140625"/>
-    <col min="13" max="13" width="40" customWidth="1"/>
-    <col min="15" max="15" width="13" customWidth="1"/>
+    <col min="12" max="12" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="12.5703125" customWidth="1"/>
-    <col min="18" max="18" width="11.42578125" customWidth="1"/>
-    <col min="19" max="19" width="12.85546875" customWidth="1"/>
+    <col min="17" max="17" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.42578125" customWidth="1"/>
+    <col min="20" max="20" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="16.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="30.75">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:32" ht="30.75">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="I1" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="12" t="s">
+      <c r="J1" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="13" t="s">
+      <c r="K1" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="13" t="s">
+      <c r="L1" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="13" t="s">
+      <c r="M1" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="13" t="s">
+      <c r="N1" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="13" t="s">
+      <c r="O1" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="13" t="s">
+      <c r="P1" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="13" t="s">
+      <c r="Q1" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="13" t="s">
+      <c r="R1" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="13" t="s">
+      <c r="S1" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="7"/>
-    </row>
-    <row r="2" spans="1:20" ht="91.5">
-      <c r="A2" s="14">
+      <c r="T1" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="25" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:32" ht="91.5">
+      <c r="A2" s="12">
         <v>96620</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" s="12">
+        <v>1499060</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="G2" s="14">
+        <v>0</v>
+      </c>
+      <c r="H2" s="14">
+        <v>300</v>
+      </c>
+      <c r="I2" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="J2" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="K2" s="15"/>
+      <c r="L2" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="M2" s="19"/>
+      <c r="N2" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="O2" s="19"/>
+      <c r="P2" s="19"/>
+      <c r="Q2" s="19"/>
+      <c r="R2" s="19"/>
+      <c r="S2" s="28"/>
+      <c r="T2" s="19"/>
+      <c r="U2" s="28"/>
+      <c r="X2" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y2" s="12"/>
+      <c r="Z2" s="12"/>
+      <c r="AA2" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB2" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="AC2" s="19"/>
+      <c r="AD2" s="12"/>
+      <c r="AE2" s="12"/>
+      <c r="AF2" s="12"/>
+    </row>
+    <row r="3" spans="1:32" ht="180.75" customHeight="1">
+      <c r="A3" s="12">
+        <v>114367</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3" s="12">
+        <v>791900</v>
+      </c>
+      <c r="E3" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="D2" s="14">
-        <v>1499060</v>
-      </c>
-      <c r="E2" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="F2" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="G2" s="16">
+      <c r="F3" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="G3" s="14"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="J3" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="K3" s="12"/>
+      <c r="L3" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="M3" s="19"/>
+      <c r="N3" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="O3" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="P3" s="19"/>
+      <c r="Q3" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="R3" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="S3" s="28"/>
+      <c r="T3" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="U3" s="28"/>
+      <c r="X3" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y3" s="12"/>
+      <c r="Z3" s="12"/>
+      <c r="AA3" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB3" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="AC3" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD3" s="12"/>
+      <c r="AE3" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="AF3" s="12" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:32" ht="212.25" customHeight="1">
+      <c r="A4" s="12">
+        <v>125243</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4" s="12">
+        <v>2362663</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="F4" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="G4" s="14">
         <v>0</v>
       </c>
-      <c r="H2" s="16">
-        <v>300</v>
-      </c>
-      <c r="I2" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="J2" s="16" t="s">
+      <c r="H4" s="14">
+        <v>1600</v>
+      </c>
+      <c r="I4" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="J4" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="K4" s="17">
+        <v>0.25</v>
+      </c>
+      <c r="L4" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="M4" s="19"/>
+      <c r="N4" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="O4" s="19"/>
+      <c r="P4" s="19"/>
+      <c r="Q4" s="19"/>
+      <c r="R4" s="19"/>
+      <c r="S4" s="28"/>
+      <c r="T4" s="19"/>
+      <c r="U4" s="28"/>
+      <c r="X4" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y4" s="12"/>
+      <c r="Z4" s="12"/>
+      <c r="AA4" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB4" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC4" s="19"/>
+      <c r="AD4" s="12"/>
+      <c r="AE4" s="12"/>
+      <c r="AF4" s="12"/>
+    </row>
+    <row r="5" spans="1:32" ht="130.5" customHeight="1">
+      <c r="A5" s="12">
+        <v>133485</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="D5" s="12">
+        <v>170000</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="F5" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="G5" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="H5" s="14">
+        <v>8</v>
+      </c>
+      <c r="I5" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="J5" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="K5" s="17">
+        <v>0.5</v>
+      </c>
+      <c r="L5" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="M5" s="19"/>
+      <c r="N5" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="O5" s="19"/>
+      <c r="P5" s="19"/>
+      <c r="Q5" s="19"/>
+      <c r="R5" s="19"/>
+      <c r="S5" s="28"/>
+      <c r="T5" s="19"/>
+      <c r="U5" s="28"/>
+      <c r="X5" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y5" s="12"/>
+      <c r="Z5" s="12"/>
+      <c r="AA5" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB5" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC5" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="AD5" s="12"/>
+      <c r="AE5" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF5" s="12" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="6" spans="1:32" ht="211.5" customHeight="1">
+      <c r="A6" s="12">
+        <v>5673</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="D6" s="12">
+        <v>3800000</v>
+      </c>
+      <c r="E6" t="s">
+        <v>56</v>
+      </c>
+      <c r="F6" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="G6" s="14">
+        <v>0</v>
+      </c>
+      <c r="H6" s="14">
+        <v>311205</v>
+      </c>
+      <c r="I6" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="J6" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="K6" s="12"/>
+      <c r="L6" s="26" t="s">
+        <v>60</v>
+      </c>
+      <c r="M6" s="19"/>
+      <c r="N6" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="O6" s="19"/>
+      <c r="P6" s="19"/>
+      <c r="Q6" s="19"/>
+      <c r="R6" s="19"/>
+      <c r="S6" s="28"/>
+      <c r="T6" s="19"/>
+      <c r="U6" s="28"/>
+      <c r="X6" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="Y6" s="12"/>
+      <c r="Z6" s="12"/>
+      <c r="AA6" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB6" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="AC6" s="19"/>
+      <c r="AD6" s="12"/>
+      <c r="AE6" s="12"/>
+      <c r="AF6" s="12"/>
+    </row>
+    <row r="7" spans="1:32" ht="178.5" customHeight="1">
+      <c r="A7" s="12">
+        <v>5323</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="D7" s="12">
+        <v>3780000</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="F7" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="G7" s="14">
+        <v>0</v>
+      </c>
+      <c r="H7" s="14">
+        <v>3487</v>
+      </c>
+      <c r="I7" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="J7" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="K7" s="12"/>
+      <c r="L7" s="26" t="s">
+        <v>60</v>
+      </c>
+      <c r="M7" s="19"/>
+      <c r="N7" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="O7" s="19"/>
+      <c r="P7" s="19"/>
+      <c r="Q7" s="19"/>
+      <c r="R7" s="19"/>
+      <c r="S7" s="28" t="s">
+        <v>65</v>
+      </c>
+      <c r="T7" s="19"/>
+      <c r="U7" s="28"/>
+      <c r="X7" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="Y7" s="12"/>
+      <c r="Z7" s="12"/>
+      <c r="AA7" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB7" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC7" s="19"/>
+      <c r="AD7" s="12"/>
+      <c r="AE7" s="12"/>
+      <c r="AF7" s="12"/>
+    </row>
+    <row r="8" spans="1:32" ht="192" customHeight="1">
+      <c r="A8" s="12">
+        <v>5285</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="D8" s="12">
+        <v>3750000</v>
+      </c>
+      <c r="E8" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="K2" s="17"/>
-      <c r="L2" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="M2" s="14"/>
-      <c r="N2" s="14"/>
-      <c r="O2" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="P2" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q2" s="14"/>
-      <c r="R2" s="14"/>
-      <c r="S2" s="14"/>
-    </row>
-    <row r="3" spans="1:20" ht="180.75" customHeight="1">
-      <c r="A3" s="14">
-        <v>114367</v>
-      </c>
-      <c r="B3" s="14" t="s">
+      <c r="F8" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="G8" s="14">
+        <v>0</v>
+      </c>
+      <c r="H8" s="14">
+        <v>5000</v>
+      </c>
+      <c r="I8" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="J8" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="K8" s="12"/>
+      <c r="L8" s="26" t="s">
+        <v>60</v>
+      </c>
+      <c r="M8" s="19"/>
+      <c r="N8" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="O8" s="19"/>
+      <c r="P8" s="19"/>
+      <c r="Q8" s="19"/>
+      <c r="R8" s="19"/>
+      <c r="S8" s="28"/>
+      <c r="T8" s="19"/>
+      <c r="U8" s="28"/>
+      <c r="X8" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="Y8" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="Z8" s="12"/>
+      <c r="AA8" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB8" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="D3" s="14">
-        <v>791900</v>
-      </c>
-      <c r="E3" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="F3" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="G3" s="16"/>
-      <c r="H3" s="16"/>
-      <c r="I3" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="J3" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="K3" s="14"/>
-      <c r="L3" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="M3" s="14"/>
-      <c r="N3" s="14"/>
-      <c r="O3" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="P3" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q3" s="14"/>
-      <c r="R3" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="S3" s="14" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20" ht="212.25" customHeight="1">
-      <c r="A4" s="14">
-        <v>125243</v>
-      </c>
-      <c r="B4" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="C4" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="D4" s="14">
-        <v>2362663</v>
-      </c>
-      <c r="E4" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="F4" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="G4" s="16">
-        <v>0</v>
-      </c>
-      <c r="H4" s="16">
-        <v>1600</v>
-      </c>
-      <c r="I4" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="J4" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="K4" s="19">
-        <v>0.25</v>
-      </c>
-      <c r="L4" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="M4" s="14"/>
-      <c r="N4" s="14"/>
-      <c r="O4" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="P4" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q4" s="14"/>
-      <c r="R4" s="14"/>
-      <c r="S4" s="14"/>
-    </row>
-    <row r="5" spans="1:20" ht="130.5" customHeight="1">
-      <c r="A5" s="14">
-        <v>133485</v>
-      </c>
-      <c r="B5" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="C5" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="D5" s="14">
-        <v>170000</v>
-      </c>
-      <c r="E5" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="F5" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="G5" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="H5" s="16"/>
-      <c r="I5" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="J5" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="K5" s="19">
-        <v>0.5</v>
-      </c>
-      <c r="L5" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="M5" s="14"/>
-      <c r="N5" s="14"/>
-      <c r="O5" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="P5" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q5" s="14"/>
-      <c r="R5" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="S5" s="14" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" ht="211.5" customHeight="1">
-      <c r="A6" s="14">
-        <v>5673</v>
-      </c>
-      <c r="B6" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="D6" s="14">
-        <v>3800000</v>
-      </c>
-      <c r="E6" t="s">
-        <v>51</v>
-      </c>
-      <c r="F6" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="G6" s="16">
-        <v>0</v>
-      </c>
-      <c r="H6" s="16">
-        <v>311205</v>
-      </c>
-      <c r="I6" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="J6" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="K6" s="14"/>
-      <c r="L6" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="M6" s="14"/>
-      <c r="N6" s="14"/>
-      <c r="O6" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="P6" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q6" s="14"/>
-      <c r="R6" s="14"/>
-      <c r="S6" s="14"/>
-    </row>
-    <row r="7" spans="1:20" ht="178.5" customHeight="1">
-      <c r="A7" s="14">
-        <v>5323</v>
-      </c>
-      <c r="B7" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="C7" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="D7" s="14">
-        <v>3780000</v>
-      </c>
-      <c r="E7" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="F7" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="G7" s="16">
-        <v>0</v>
-      </c>
-      <c r="H7" s="16">
-        <v>3487</v>
-      </c>
-      <c r="I7" s="18" t="s">
-        <v>59</v>
-      </c>
-      <c r="J7" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="K7" s="14"/>
-      <c r="L7" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="M7" s="14"/>
-      <c r="N7" s="14"/>
-      <c r="O7" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="P7" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q7" s="14"/>
-      <c r="R7" s="14"/>
-      <c r="S7" s="14"/>
-    </row>
-    <row r="8" spans="1:20" ht="192" customHeight="1">
-      <c r="A8" s="14">
-        <v>5285</v>
-      </c>
-      <c r="B8" s="14" t="s">
-        <v>60</v>
-      </c>
-      <c r="C8" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="D8" s="14">
-        <v>3750000</v>
-      </c>
-      <c r="E8" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="F8" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="G8" s="16">
-        <v>0</v>
-      </c>
-      <c r="H8" s="16">
-        <v>5000</v>
-      </c>
-      <c r="I8" s="18" t="s">
-        <v>62</v>
-      </c>
-      <c r="J8" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="K8" s="14"/>
-      <c r="L8" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="M8" s="20" t="s">
-        <v>63</v>
-      </c>
-      <c r="N8" s="14"/>
-      <c r="O8" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="P8" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q8" s="14"/>
-      <c r="R8" s="14"/>
-      <c r="S8" s="14"/>
+      <c r="AC8" s="19"/>
+      <c r="AD8" s="12"/>
+      <c r="AE8" s="12"/>
+      <c r="AF8" s="12"/>
     </row>
   </sheetData>
-  <dataValidations count="5">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S8" xr:uid="{AAACC25B-A949-4DDD-8867-9532C127C28E}">
+  <dataValidations count="12">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AF2:AF8" xr:uid="{AAACC25B-A949-4DDD-8867-9532C127C28E}">
       <formula1>"Electricity Access, Energy Efficiency, Renewable EnergyEnergy Infrastructure,   Transport, Digital &amp; Data, Clean Cooking, Decarbonization, Hydrogen, Off-Grid, On-Grid"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R8" xr:uid="{05155D34-D30F-4103-AD8C-EC4F7E59FEF3}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AE2:AE8 Q2:Q8" xr:uid="{05155D34-D30F-4103-AD8C-EC4F7E59FEF3}">
       <formula1>"NDC Support, National Strategy, Legal Framework,Incentives and Support, Government Capacity-Building, Carbon Pricing and Monitoring, Financing Model, Business Model"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q8" xr:uid="{9A02947A-07E4-4B49-BEFB-D5566767A8A4}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AD2:AD8 P2:P8" xr:uid="{9A02947A-07E4-4B49-BEFB-D5566767A8A4}">
       <formula1>"AMP, PUDC, Solar4Health, Action Opportunities, Italy UNDP Energy Partnership"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P8" xr:uid="{D24118CD-5D98-4EE3-BF1A-1BEB7F719DE3}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AB2:AB8" xr:uid="{D24118CD-5D98-4EE3-BF1A-1BEB7F719DE3}">
       <formula1>"Electricity Access, Energy Efficiency, Clean Cooking, Renewable Energy"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O8" xr:uid="{076AD55B-6EA8-423E-A600-4923F76B33E3}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AA2:AA8 N2:N8" xr:uid="{076AD55B-6EA8-423E-A600-4923F76B33E3}">
       <formula1>"Accelerating just energy transition, Close the gap on energy access, Scale up energy finance"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AC2:AC8" xr:uid="{9555CC12-21E5-4C0A-8153-A2205FEC65BB}">
+      <formula1>"Tier 1, Tier 2, Tier 3"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O8" xr:uid="{C30F9077-9B12-48C6-B450-BBAB32EC3044}">
+      <formula1>"Electricity Access, Energy Efficiency, Clean Cooking, Renewable Energy, Overall"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2:M8" xr:uid="{25366306-132E-4CD6-892B-74ED5302AF55}">
+      <formula1>"Finance, Gender, Efficiency, Just, Health"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:T8" xr:uid="{6FAFD493-5BFA-4997-B379-34B1AA63DE66}">
+      <formula1>"National, Regional, City, Community"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L8" xr:uid="{26364F1C-E76B-4723-9EE2-8361ED65D552}">
+      <formula1>"Non-VF, VF"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R8" xr:uid="{ABABE75B-D97C-4A29-8415-F3F867F831D6}">
+      <formula1>"Electricity Access, Energy Efficiency, Renewable Energy, Infrastructure,  Transport, Digital &amp; Data, Clean Cooking, Decarbonization, Hydrogen, Off-Grid, On-Grid, Research &amp; Innovation, Grant &amp; Investment"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S8" xr:uid="{67934836-BF33-439A-86C6-63226ADD98C9}">
+      <formula1>"Solar, Wind, Bioenergy, Hydro, Geothermal, Waste, Some Sources, Other, Unknown"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
@@ -1471,12 +1713,18 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{F4095BA4-885E-4932-AB11-7C8DA350D7B2}">
           <x14:formula1>
-            <xm:f>'Beneficiary Categories'!$B$2:$B$16</xm:f>
+            <xm:f>'Beneficiary Categories'!$A$2:$A$16</xm:f>
           </x14:formula1>
-          <xm:sqref>E2:E13</xm:sqref>
+          <xm:sqref>E9:E13</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D64998FB-B8EF-4CA8-8729-BE53A7F83E14}">
+          <x14:formula1>
+            <xm:f>'Beneficiary Categories'!$A$2:$A$22</xm:f>
+          </x14:formula1>
+          <xm:sqref>E2:E8</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1533,51 +1781,51 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="K1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="7"/>
-      <c r="O1" s="7" t="s">
+      <c r="L1" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="M1" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="N1" s="5"/>
+      <c r="O1" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="7" t="s">
+      <c r="Q1" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="7" t="s">
+      <c r="R1" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="7" t="s">
+      <c r="S1" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="T1" s="7"/>
+      <c r="T1" s="5"/>
     </row>
     <row r="2" spans="1:20" ht="91.5">
       <c r="A2">
         <v>96620</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D2">
         <v>1499060</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="G2" s="3">
         <v>0</v>
@@ -1585,21 +1833,21 @@
       <c r="H2" s="3">
         <v>300</v>
       </c>
-      <c r="I2" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="J2" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="K2" s="8"/>
+      <c r="I2" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="K2" s="6"/>
       <c r="L2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="O2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="P2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:20" ht="231" customHeight="1">
@@ -1607,42 +1855,42 @@
         <v>114367</v>
       </c>
       <c r="B3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D3">
         <v>791900</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4" t="s">
         <v>32</v>
       </c>
+      <c r="J3" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="L3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="O3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="P3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="R3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:20" ht="241.5" customHeight="1">
@@ -1650,19 +1898,19 @@
         <v>125243</v>
       </c>
       <c r="B4" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D4">
         <v>2362663</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>37</v>
+        <v>72</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>40</v>
       </c>
       <c r="G4" s="3">
         <v>0</v>
@@ -1670,23 +1918,23 @@
       <c r="H4" s="3">
         <v>1600</v>
       </c>
-      <c r="I4" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="J4" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="K4" s="10">
+      <c r="I4" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="K4" s="8">
         <v>0.25</v>
       </c>
       <c r="L4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="O4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="P4" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:20" ht="289.5" customHeight="1">
@@ -1694,47 +1942,47 @@
         <v>133485</v>
       </c>
       <c r="B5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D5">
         <v>170000</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F5" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="K5" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="L5" t="s">
+        <v>26</v>
+      </c>
+      <c r="O5" t="s">
+        <v>27</v>
+      </c>
+      <c r="P5" t="s">
         <v>43</v>
       </c>
-      <c r="G5" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="J5" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="K5" s="10">
-        <v>0.5</v>
-      </c>
-      <c r="L5" t="s">
-        <v>24</v>
-      </c>
-      <c r="O5" t="s">
-        <v>25</v>
-      </c>
-      <c r="P5" t="s">
-        <v>40</v>
-      </c>
       <c r="R5" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="S5" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:20" ht="229.5">
@@ -1742,40 +1990,40 @@
         <v>5673</v>
       </c>
       <c r="B6" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C6" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D6">
         <v>3800000</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="G6" s="6">
+        <v>73</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="G6" s="4">
         <v>0</v>
       </c>
-      <c r="H6" s="6">
+      <c r="H6" s="4">
         <v>311205</v>
       </c>
-      <c r="I6" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="J6" s="6" t="s">
-        <v>54</v>
+      <c r="I6" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>59</v>
       </c>
       <c r="L6" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="O6" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="P6" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:20" ht="178.5" customHeight="1">
@@ -1783,19 +2031,19 @@
         <v>5323</v>
       </c>
       <c r="B7" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C7" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D7">
         <v>3780000</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>58</v>
+        <v>62</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>63</v>
       </c>
       <c r="G7" s="3">
         <v>0</v>
@@ -1803,20 +2051,20 @@
       <c r="H7" s="3">
         <v>3487</v>
       </c>
-      <c r="I7" s="9" t="s">
+      <c r="I7" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="J7" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="J7" s="6" t="s">
-        <v>54</v>
-      </c>
       <c r="L7" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="O7" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="P7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:20" ht="210" customHeight="1">
@@ -1824,19 +2072,19 @@
         <v>5285</v>
       </c>
       <c r="B8" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="C8" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D8">
         <v>3750000</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>61</v>
+        <v>23</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>67</v>
       </c>
       <c r="G8" s="3">
         <v>0</v>
@@ -1844,23 +2092,23 @@
       <c r="H8" s="3">
         <v>5000</v>
       </c>
-      <c r="I8" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="J8" s="6" t="s">
-        <v>54</v>
+      <c r="I8" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>59</v>
       </c>
       <c r="L8" t="s">
-        <v>55</v>
-      </c>
-      <c r="M8" s="11" t="s">
-        <v>63</v>
+        <v>60</v>
+      </c>
+      <c r="M8" s="9" t="s">
+        <v>69</v>
       </c>
       <c r="O8" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="P8" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -1893,7 +2141,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{A64EAE38-84EC-4F5F-BE42-F964F4CD03BF}">
           <x14:formula1>
-            <xm:f>'Beneficiary Categories'!$B$2:$B$16</xm:f>
+            <xm:f>'Beneficiary Categories'!$A$2:$A$16</xm:f>
           </x14:formula1>
           <xm:sqref>E2:E13</xm:sqref>
         </x14:dataValidation>
@@ -1950,8 +2198,8 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="7" t="s">
-        <v>12</v>
+      <c r="K1" s="5" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="238.5" customHeight="1">
@@ -1959,19 +2207,19 @@
         <v>96620</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D2">
         <v>1499060</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>66</v>
+        <v>23</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>74</v>
       </c>
       <c r="G2" s="3">
         <v>0</v>
@@ -1979,14 +2227,14 @@
       <c r="H2" s="3">
         <v>300</v>
       </c>
-      <c r="I2" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="J2" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="K2" s="8" t="s">
-        <v>67</v>
+      <c r="I2" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="K2" s="6" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="231" customHeight="1">
@@ -1994,31 +2242,31 @@
         <v>114367</v>
       </c>
       <c r="B3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D3">
         <v>791900</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="I3" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="G3" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="I3" s="4" t="s">
         <v>32</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="241.5" customHeight="1">
@@ -2026,19 +2274,19 @@
         <v>125243</v>
       </c>
       <c r="B4" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D4">
         <v>2362663</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>37</v>
+        <v>72</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>40</v>
       </c>
       <c r="G4" s="3">
         <v>0</v>
@@ -2046,11 +2294,11 @@
       <c r="H4" s="3">
         <v>1600</v>
       </c>
-      <c r="I4" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="J4" s="6" t="s">
-        <v>39</v>
+      <c r="I4" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="289.5" customHeight="1">
@@ -2058,31 +2306,31 @@
         <v>133485</v>
       </c>
       <c r="B5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D5">
         <v>170000</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="J5" s="6" t="s">
-        <v>46</v>
+        <v>73</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="229.5">
@@ -2090,31 +2338,31 @@
         <v>5673</v>
       </c>
       <c r="B6" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C6" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D6">
         <v>3800000</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="G6" s="6">
+        <v>73</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="G6" s="4">
         <v>0</v>
       </c>
-      <c r="H6" s="6">
+      <c r="H6" s="4">
         <v>1433</v>
       </c>
-      <c r="I6" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="J6" s="6" t="s">
-        <v>54</v>
+      <c r="I6" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="178.5" customHeight="1">
@@ -2122,19 +2370,19 @@
         <v>5323</v>
       </c>
       <c r="B7" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C7" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D7">
         <v>3780000</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>72</v>
+        <v>62</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>80</v>
       </c>
       <c r="G7" s="3">
         <v>0</v>
@@ -2142,11 +2390,11 @@
       <c r="H7" s="3">
         <v>4863</v>
       </c>
-      <c r="I7" s="9" t="s">
+      <c r="I7" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="J7" s="4" t="s">
         <v>59</v>
-      </c>
-      <c r="J7" s="6" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="210" customHeight="1">
@@ -2154,19 +2402,19 @@
         <v>5285</v>
       </c>
       <c r="B8" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="C8" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D8">
         <v>3750000</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>61</v>
+        <v>23</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>67</v>
       </c>
       <c r="G8" s="3">
         <v>0</v>
@@ -2174,11 +2422,11 @@
       <c r="H8" s="3">
         <v>5000</v>
       </c>
-      <c r="I8" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="J8" s="6" t="s">
-        <v>54</v>
+      <c r="I8" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -2194,7 +2442,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000000000000}">
           <x14:formula1>
-            <xm:f>'Beneficiary Categories'!$B$2:$B$16</xm:f>
+            <xm:f>'Beneficiary Categories'!$A$2:$A$16</xm:f>
           </x14:formula1>
           <xm:sqref>E2:E13</xm:sqref>
         </x14:dataValidation>
@@ -2206,177 +2454,189 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="3" width="52.7109375" customWidth="1"/>
+    <col min="1" max="2" width="52.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:2">
+      <c r="A1" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="20" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="45.75">
+      <c r="A2" s="29" t="s">
+        <v>62</v>
+      </c>
+      <c r="B2" s="21" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="29" t="s">
+        <v>82</v>
+      </c>
+      <c r="B3" s="21" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="30.75">
+      <c r="A4" s="29" t="s">
+        <v>84</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="30.75">
+      <c r="A5" s="29" t="s">
+        <v>86</v>
+      </c>
+      <c r="B5" s="21" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="91.5">
+      <c r="A6" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="B6" s="21" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="45.75">
+      <c r="A7" s="29" t="s">
+        <v>90</v>
+      </c>
+      <c r="B7" s="21" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="45.75">
+      <c r="A8" s="29" t="s">
+        <v>92</v>
+      </c>
+      <c r="B8" s="21" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="45.75">
+      <c r="A9" s="29" t="s">
+        <v>94</v>
+      </c>
+      <c r="B9" s="21" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="30.75">
+      <c r="A10" s="29" t="s">
+        <v>96</v>
+      </c>
+      <c r="B10" s="30" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="30.75">
+      <c r="A11" s="29" t="s">
+        <v>98</v>
+      </c>
+      <c r="B11" s="30" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="45.75">
+      <c r="A12" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="B12" s="21" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="30.75">
+      <c r="A13" s="29" t="s">
         <v>73</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="21" t="s">
-        <v>75</v>
-      </c>
-      <c r="B2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="21"/>
-      <c r="B3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C3" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="21"/>
-      <c r="B4" t="s">
-        <v>79</v>
-      </c>
-      <c r="C4" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="22" t="s">
-        <v>81</v>
-      </c>
-      <c r="B5" t="s">
-        <v>82</v>
-      </c>
-      <c r="C5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="22"/>
-      <c r="B6" t="s">
-        <v>84</v>
-      </c>
-      <c r="C6" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="22"/>
-      <c r="B7" t="s">
-        <v>86</v>
-      </c>
-      <c r="C7" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="22"/>
-      <c r="B8" t="s">
-        <v>88</v>
-      </c>
-      <c r="C8" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="22"/>
-      <c r="B9" t="s">
-        <v>65</v>
-      </c>
-      <c r="C9" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="23" t="s">
-        <v>91</v>
-      </c>
-      <c r="B10" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="23"/>
-      <c r="B11" t="s">
-        <v>93</v>
-      </c>
-      <c r="C11" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="24" t="s">
-        <v>95</v>
-      </c>
-      <c r="B12" t="s">
-        <v>64</v>
-      </c>
-      <c r="C12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="24"/>
-      <c r="B13" t="s">
-        <v>36</v>
-      </c>
-      <c r="C13" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="24"/>
-      <c r="B14" t="s">
-        <v>98</v>
-      </c>
-      <c r="C14" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="B15" t="s">
-        <v>29</v>
-      </c>
-      <c r="C15" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="5" t="s">
+      <c r="B13" s="30" t="s">
         <v>102</v>
       </c>
-      <c r="B16" t="s">
-        <v>102</v>
-      </c>
-      <c r="C16" t="s">
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="29" t="s">
         <v>103</v>
       </c>
+      <c r="B14" s="30" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="30.75">
+      <c r="A15" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="30" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="30.75">
+      <c r="A16" s="29" t="s">
+        <v>46</v>
+      </c>
+      <c r="B16" s="30" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="30.75">
+      <c r="A17" s="29" t="s">
+        <v>107</v>
+      </c>
+      <c r="B17" s="21" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="30.75">
+      <c r="A18" s="29" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="30" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="76.5">
+      <c r="A19" s="29" t="s">
+        <v>110</v>
+      </c>
+      <c r="B19" s="30" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="30.75">
+      <c r="A20" s="29" t="s">
+        <v>112</v>
+      </c>
+      <c r="B20" s="30" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="45.75">
+      <c r="A21" s="29" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="31" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="30.75">
+      <c r="A22" s="29" t="s">
+        <v>115</v>
+      </c>
+      <c r="B22" s="30" t="s">
+        <v>116</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A2:A4"/>
-    <mergeCell ref="A5:A9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A12:A14"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2631,6 +2891,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
@@ -2641,23 +2910,14 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B2021D64-63CF-41B0-AAED-0CD8BAFB5D20}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D95151FA-9580-4149-A82E-5CCA90355502}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EF0F2F1F-F7E8-4442-9517-DECF66C4186C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EF0F2F1F-F7E8-4442-9517-DECF66C4186C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D95151FA-9580-4149-A82E-5CCA90355502}"/>
 </file>
--- a/01_Input/00_CO Validation/Turkey - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Turkey - Energy Projects.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27226"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28318"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ben/Documents/UNDP/Energy/CO Validation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="305" documentId="13_ncr:1_{0EFF3E03-FAB0-5547-AB89-E48C983D93AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DAA81A35-2EC1-4946-BF43-BA369B9FE81B}"/>
+  <xr:revisionPtr revIDLastSave="319" documentId="13_ncr:1_{0EFF3E03-FAB0-5547-AB89-E48C983D93AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FE066466-46E0-41B5-9061-A0E51774F24B}"/>
   <bookViews>
-    <workbookView xWindow="7500" yWindow="740" windowWidth="16100" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7500" yWindow="740" windowWidth="16100" windowHeight="9660" firstSheet="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projects (3)" sheetId="4" r:id="rId1"/>
-    <sheet name="Projects (2)" sheetId="3" r:id="rId2"/>
-    <sheet name="Projects" sheetId="1" r:id="rId3"/>
+    <sheet name="Projects (2)" sheetId="3" state="hidden" r:id="rId2"/>
+    <sheet name="Projects" sheetId="1" state="hidden" r:id="rId3"/>
     <sheet name="Beneficiary Categories" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191028"/>
@@ -38,8 +38,35 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={568BB6AF-B8CD-4C43-9C97-518549B621AC}</author>
+    <author>tc={69FD3DF8-97B7-4D52-AB86-567EE31AE725}</author>
+  </authors>
+  <commentList>
+    <comment ref="H6" authorId="0" shapeId="0" xr:uid="{568BB6AF-B8CD-4C43-9C97-518549B621AC}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    I moved the data to notes as this value ( number of motors) is not recognized by our system. Please see tab " beneficiary categories for more information</t>
+      </text>
+    </comment>
+    <comment ref="H8" authorId="1" shapeId="0" xr:uid="{69FD3DF8-97B7-4D52-AB86-567EE31AE725}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    I moved the data to notes as this value ( number of motors) is not recognized by our system. Please see tab " beneficiary categories for more information</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="119">
   <si>
     <t>Project ID</t>
   </si>
@@ -276,11 +303,20 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t>-Policy, Legislative, and Regulatory Support 
+      <t xml:space="preserve">-Policy, Legislative, and Regulatory Support 
 -Strengthening of Institutional Support within the Ministry of Agriculture and Forestry and GDF for supporting construction from wood in Türkiye
 -Operationalization of Phased Financial Support Mechanism (FSM)  and provision of incentives to SMEs for greater use of wood in construction in Türkiye
 -Increasing awareness about the benefits of using wood in construction
--Increasing training and capacity building on using wood in construction</t>
+-Increasing training and capacity building on using wood in construction
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>GHG Emission Reduction= 311205</t>
     </r>
   </si>
   <si>
@@ -370,6 +406,99 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
       </rPr>
+      <t xml:space="preserve">-Conduction of efficiency audits and preparation of invesment plans for SMEs
+-Ongoing scaling up/dissemination of successfully completed pilot implementation with KOSGEB
+-Training of manufacturers and end-users (SMEs)
+-Harmonization of Turkish policies, regulations and standards applicable to motors with EU Eco-design standards
+-Capacity building for testing motors at TSI labs
+-Promotional and awareness raising activities
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Cumulative number of phased out inefficient electric motors taken into a recycling program by EOP=5000</t>
+    </r>
+  </si>
+  <si>
+    <t>to the CO: Please estimate number of beneficiaries.</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Comments</t>
+  </si>
+  <si>
+    <t>Capacity Training</t>
+  </si>
+  <si>
+    <t>Other Energy Services</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">Realization: Project to kick off in 2023.
+# of direct beneficiaries targeted: 900
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">Other outputs:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>-Policy, Legislative, and Regulatory Support 
+-Strengthening of Institutional Support within the Ministry of Agriculture and Forestry and GDF for supporting construction from wood in Türkiye
+-Operationalization of Phased Financial Support Mechanism (FSM)  and provision of incentives to SMEs for greater use of wood in construction in Türkiye
+-Increasing awareness about the benefits of using wood in construction
+-Increasing training and capacity building on using wood in construction</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">Realization: 357
+SMEs replaced inefficient motors: 48
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">Other outputs:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
       <t>-Conduction of efficiency audits and preparation of invesment plans for SMEs
 -Ongoing scaling up/dissemination of successfully completed pilot implementation with KOSGEB
 -Training of manufacturers and end-users (SMEs)
@@ -377,21 +506,6 @@
 -Capacity building for testing motors at TSI labs
 -Promotional and awareness raising activities</t>
     </r>
-  </si>
-  <si>
-    <t>to the CO: Please estimate number of beneficiaries.</t>
-  </si>
-  <si>
-    <t>Category</t>
-  </si>
-  <si>
-    <t>Comments</t>
-  </si>
-  <si>
-    <t>Capacity Training</t>
-  </si>
-  <si>
-    <t>Other Energy Services</t>
   </si>
   <si>
     <t># of pilot projects at farm and enterprise levels on resource efficiency in agriculture and agro-industries</t>
@@ -546,7 +660,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -617,6 +731,11 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="3">
@@ -828,6 +947,12 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Folashade Jaiyeola" id="{8A2E3BA9-905C-408C-84FA-C6220F80059D}" userId="S::folashade.jaiyeola@undp.org::c208a32e-6303-48b2-9538-645490e99643" providerId="AD"/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1115,8 +1240,19 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="H6" dT="2024-11-22T19:28:37.03" personId="{8A2E3BA9-905C-408C-84FA-C6220F80059D}" id="{568BB6AF-B8CD-4C43-9C97-518549B621AC}">
+    <text>I moved the data to notes as this value ( number of motors) is not recognized by our system. Please see tab " beneficiary categories for more information</text>
+  </threadedComment>
+  <threadedComment ref="H8" dT="2024-11-22T19:28:30.00" personId="{8A2E3BA9-905C-408C-84FA-C6220F80059D}" id="{69FD3DF8-97B7-4D52-AB86-567EE31AE725}">
+    <text>I moved the data to notes as this value ( number of motors) is not recognized by our system. Please see tab " beneficiary categories for more information</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC7FC47B-9AC6-462B-BC07-1DA627AEFE8D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC7FC47B-9AC6-462B-BC07-1DA627AEFE8D}">
   <dimension ref="A1:AF8"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
@@ -1497,9 +1633,7 @@
       <c r="G6" s="14">
         <v>0</v>
       </c>
-      <c r="H6" s="14">
-        <v>311205</v>
-      </c>
+      <c r="H6" s="14"/>
       <c r="I6" s="16" t="s">
         <v>58</v>
       </c>
@@ -1623,9 +1757,7 @@
       <c r="G8" s="14">
         <v>0</v>
       </c>
-      <c r="H8" s="14">
-        <v>5000</v>
-      </c>
+      <c r="H8" s="14"/>
       <c r="I8" s="16" t="s">
         <v>68</v>
       </c>
@@ -1711,6 +1843,7 @@
     <hyperlink ref="C5" r:id="rId4" xr:uid="{94B13E90-12AC-450B-95A5-975F7BD81E21}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId5"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
@@ -2011,7 +2144,7 @@
         <v>311205</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="J6" s="4" t="s">
         <v>59</v>
@@ -2093,7 +2226,7 @@
         <v>5000</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="J8" s="4" t="s">
         <v>59</v>
@@ -2219,7 +2352,7 @@
         <v>23</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G2" s="3">
         <v>0</v>
@@ -2234,7 +2367,7 @@
         <v>25</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="231" customHeight="1">
@@ -2257,10 +2390,10 @@
         <v>31</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="I3" s="4" t="s">
         <v>32</v>
@@ -2324,7 +2457,7 @@
         <v>48</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="I5" s="4" t="s">
         <v>49</v>
@@ -2350,7 +2483,7 @@
         <v>73</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G6" s="4">
         <v>0</v>
@@ -2359,7 +2492,7 @@
         <v>1433</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="J6" s="4" t="s">
         <v>59</v>
@@ -2382,7 +2515,7 @@
         <v>62</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G7" s="3">
         <v>0</v>
@@ -2423,7 +2556,7 @@
         <v>5000</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="J8" s="4" t="s">
         <v>59</v>
@@ -2473,87 +2606,87 @@
         <v>62</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="29" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="30.75">
       <c r="A4" s="29" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="30.75">
       <c r="A5" s="29" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="91.5">
       <c r="A6" s="29" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B6" s="21" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="45.75">
       <c r="A7" s="29" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B7" s="21" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="45.75">
       <c r="A8" s="29" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="45.75">
       <c r="A9" s="29" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B9" s="21" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="30.75">
       <c r="A10" s="29" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B10" s="30" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="30.75">
       <c r="A11" s="29" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B11" s="30" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="45.75">
       <c r="A12" s="29" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B12" s="21" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="30.75">
@@ -2561,15 +2694,15 @@
         <v>73</v>
       </c>
       <c r="B13" s="30" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="29" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B14" s="30" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="30.75">
@@ -2577,7 +2710,7 @@
         <v>23</v>
       </c>
       <c r="B15" s="30" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="30.75">
@@ -2585,15 +2718,15 @@
         <v>46</v>
       </c>
       <c r="B16" s="30" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="30.75">
       <c r="A17" s="29" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B17" s="21" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="30.75">
@@ -2601,23 +2734,23 @@
         <v>39</v>
       </c>
       <c r="B18" s="30" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="76.5">
       <c r="A19" s="29" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B19" s="30" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="30.75">
       <c r="A20" s="29" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B20" s="30" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="45.75">
@@ -2625,15 +2758,15 @@
         <v>19</v>
       </c>
       <c r="B21" s="31" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="30.75">
       <c r="A22" s="29" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B22" s="30" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
   </sheetData>
@@ -2642,8 +2775,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0d2b1cfbe0bead55dc04bff20486709a">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a3ed273af6605fa6a207dd3965c2d078" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="dd25160c21e587dbb66203dfb8c7aa52">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="05ccd5be12d50c438f9536854e894bcb" ns2:_="" ns3:_="">
     <xsd:import namespace="720239d0-7d3a-4257-bb40-a2a3b1409bb2"/>
     <xsd:import namespace="fb9e4d32-074f-4c04-81ef-e811753dfd59"/>
     <xsd:element name="properties">
@@ -2668,6 +2801,7 @@
                 <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
                 <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -2747,6 +2881,11 @@
     <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
@@ -2911,7 +3050,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B2021D64-63CF-41B0-AAED-0CD8BAFB5D20}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{714679B5-20C4-4443-8DC8-90F2904D52D0}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>

--- a/01_Input/00_CO Validation/Turkey - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Turkey - Energy Projects.xlsx
@@ -215,7 +215,7 @@
       <protection locked="0" hidden="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -299,9 +299,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -390,11 +387,32 @@
 <file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
+    <author>CO validation update</author>
     <author>tc={568BB6AF-B8CD-4C43-9C97-518549B621AC}</author>
     <author>tc={69FD3DF8-97B7-4D52-AB86-567EE31AE725}</author>
   </authors>
   <commentList>
-    <comment ref="L8" authorId="0" shapeId="0">
+    <comment ref="K3" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="L3" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="K7" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="L7" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="L8" authorId="1" shapeId="0">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -402,7 +420,17 @@
     I moved the data to notes as this value ( number of motors) is not recognized by our system. Please see tab " beneficiary categories for more information</t>
       </text>
     </comment>
-    <comment ref="L11" authorId="1" shapeId="0">
+    <comment ref="K10" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="L10" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="L11" authorId="2" shapeId="0">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -960,15 +988,11 @@
           <t>Installed capacity in MW for access/productive-use outputs</t>
         </is>
       </c>
-      <c r="K3" s="14" t="n">
+      <c r="K3" s="32" t="n">
         <v>0</v>
       </c>
       <c r="L3" s="32" t="n"/>
-      <c r="M3" s="32" t="inlineStr">
-        <is>
-          <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
-        </is>
-      </c>
+      <c r="M3" s="14" t="n"/>
       <c r="N3" s="14" t="n"/>
       <c r="O3" s="15" t="n"/>
       <c r="P3" s="19" t="n"/>
@@ -1322,15 +1346,11 @@
           <t>Installed capacity in MW for access/productive-use outputs</t>
         </is>
       </c>
-      <c r="K7" s="14" t="n">
+      <c r="K7" s="32" t="n">
         <v>0</v>
       </c>
       <c r="L7" s="32" t="n"/>
-      <c r="M7" s="32" t="inlineStr">
-        <is>
-          <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
-        </is>
-      </c>
+      <c r="M7" s="14" t="n"/>
       <c r="N7" s="14" t="n"/>
       <c r="O7" s="17" t="n"/>
       <c r="P7" s="19" t="n"/>
@@ -1564,15 +1584,11 @@
           <t>Installed capacity in MW for access/productive-use outputs</t>
         </is>
       </c>
-      <c r="K10" s="14" t="n">
+      <c r="K10" s="32" t="n">
         <v>0</v>
       </c>
       <c r="L10" s="32" t="n"/>
-      <c r="M10" s="33" t="inlineStr">
-        <is>
-          <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
-        </is>
-      </c>
+      <c r="M10" s="16" t="n"/>
       <c r="N10" s="14" t="n"/>
       <c r="O10" s="12" t="n"/>
       <c r="P10" s="19" t="n"/>
@@ -1693,7 +1709,7 @@
       <c r="AI11" s="12" t="n"/>
     </row>
   </sheetData>
-  <dataValidations count="15">
+  <dataValidations count="13">
     <dataValidation sqref="AF2:AF8" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Electricity Access, Energy Efficiency, Renewable EnergyEnergy Infrastructure,   Transport, Digital &amp; Data, Clean Cooking, Decarbonization, Hydrogen, Off-Grid, On-Grid"</formula1>
     </dataValidation>
@@ -1729,12 +1745,6 @@
     </dataValidation>
     <dataValidation sqref="S2:S8" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Solar, Wind, Bioenergy, Hydro, Geothermal, Waste, Some Sources, Other, Unknown"</formula1>
-    </dataValidation>
-    <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
-      <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
-    </dataValidation>
-    <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
-      <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
     </dataValidation>
     <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
       <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
@@ -2830,288 +2840,288 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="34" t="inlineStr">
+      <c r="A1" s="33" t="inlineStr">
         <is>
           <t>Beneficiary Category</t>
         </is>
       </c>
-      <c r="B1" s="34" t="inlineStr">
+      <c r="B1" s="33" t="inlineStr">
         <is>
           <t>Indicator</t>
         </is>
       </c>
     </row>
     <row r="2" ht="45.75" customHeight="1">
-      <c r="A2" s="35" t="inlineStr">
+      <c r="A2" s="34" t="inlineStr">
         <is>
           <t>Electricity Access</t>
         </is>
       </c>
-      <c r="B2" s="35" t="inlineStr">
+      <c r="B2" s="34" t="inlineStr">
         <is>
           <t>Number of people, disaggregated by sex, who gain access to clean electricity (direct access to electricity, lighting, cooling, etc.).</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="35" t="inlineStr">
+      <c r="A3" s="34" t="inlineStr">
         <is>
           <t>Energy (MW added)</t>
         </is>
       </c>
-      <c r="B3" s="35" t="inlineStr">
+      <c r="B3" s="34" t="inlineStr">
         <is>
           <t>Installed renewable or clean-energy power capacity added, in MW.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="30.75" customHeight="1">
-      <c r="A4" s="35" t="inlineStr">
+      <c r="A4" s="34" t="inlineStr">
         <is>
           <t>Energy Storage (MW)</t>
         </is>
       </c>
-      <c r="B4" s="35" t="inlineStr">
+      <c r="B4" s="34" t="inlineStr">
         <is>
           <t>Installed energy storage power capacity added, in MW.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30.75" customHeight="1">
-      <c r="A5" s="35" t="inlineStr">
+      <c r="A5" s="34" t="inlineStr">
         <is>
           <t>Clean Cooking</t>
         </is>
       </c>
-      <c r="B5" s="35" t="inlineStr">
+      <c r="B5" s="34" t="inlineStr">
         <is>
           <t>Number of people who gain access to clean cooking (direct access to clean cook stoves, clean fuels, biomass, etc.).</t>
         </is>
       </c>
     </row>
     <row r="6" ht="91.5" customHeight="1">
-      <c r="A6" s="35" t="inlineStr">
+      <c r="A6" s="34" t="inlineStr">
         <is>
           <t>Clean Heating</t>
         </is>
       </c>
-      <c r="B6" s="35" t="inlineStr">
+      <c r="B6" s="34" t="inlineStr">
         <is>
           <t>Number of people who gain access to clean heating (direct access to clean electric heaters, clean fuels, etc.).</t>
         </is>
       </c>
     </row>
     <row r="7" ht="45.75" customHeight="1">
-      <c r="A7" s="35" t="inlineStr">
+      <c r="A7" s="34" t="inlineStr">
         <is>
           <t>Agriculture and Food System</t>
         </is>
       </c>
-      <c r="B7" s="35" t="inlineStr">
+      <c r="B7" s="34" t="inlineStr">
         <is>
           <t>Number of people who gain access to clean, affordable, and sustainable energy for agricultural and food-system activities.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="45.75" customHeight="1">
-      <c r="A8" s="35" t="inlineStr">
+      <c r="A8" s="34" t="inlineStr">
         <is>
           <t>Health Services</t>
         </is>
       </c>
-      <c r="B8" s="35" t="inlineStr">
+      <c r="B8" s="34" t="inlineStr">
         <is>
           <t>Number of people who gain access to health care facilities through clean energy systems.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="45.75" customHeight="1">
-      <c r="A9" s="35" t="inlineStr">
+      <c r="A9" s="34" t="inlineStr">
         <is>
           <t>Water Services</t>
         </is>
       </c>
-      <c r="B9" s="35" t="inlineStr">
+      <c r="B9" s="34" t="inlineStr">
         <is>
           <t>Number of people who gain access to water services through clean energy systems.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30.75" customHeight="1">
-      <c r="A10" s="35" t="inlineStr">
+      <c r="A10" s="34" t="inlineStr">
         <is>
           <t>Education Services</t>
         </is>
       </c>
-      <c r="B10" s="35" t="inlineStr">
+      <c r="B10" s="34" t="inlineStr">
         <is>
           <t>Number of people who gain access to education services through clean energy systems, including students and teachers.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="30.75" customHeight="1">
-      <c r="A11" s="35" t="inlineStr">
+      <c r="A11" s="34" t="inlineStr">
         <is>
           <t>Transportation and E-mobility Services</t>
         </is>
       </c>
-      <c r="B11" s="35" t="inlineStr">
+      <c r="B11" s="34" t="inlineStr">
         <is>
           <t>Number of people served or energy saved from transport and e-mobility interventions, such as electric vehicles or charging stations.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="45.75" customHeight="1">
-      <c r="A12" s="35" t="inlineStr">
+      <c r="A12" s="34" t="inlineStr">
         <is>
           <t>Energy Efficiency Services</t>
         </is>
       </c>
-      <c r="B12" s="35" t="inlineStr">
+      <c r="B12" s="34" t="inlineStr">
         <is>
           <t>Energy saved from energy-efficiency interventions, such as building or industrial efficiency.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30.75" customHeight="1">
-      <c r="A13" s="35" t="inlineStr">
+      <c r="A13" s="34" t="inlineStr">
         <is>
           <t>Energy Infrastructure Services</t>
         </is>
       </c>
-      <c r="B13" s="35" t="inlineStr">
+      <c r="B13" s="34" t="inlineStr">
         <is>
           <t>Number of people benefiting from energy infrastructure interventions, such as streetlights, transmission, and distribution lines.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="35" t="inlineStr">
+      <c r="A14" s="34" t="inlineStr">
         <is>
           <t>Other Energy Services</t>
         </is>
       </c>
-      <c r="B14" s="35" t="inlineStr">
+      <c r="B14" s="34" t="inlineStr">
         <is>
           <t>Access to other energy services not captured by the categories above.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="30.75" customHeight="1">
-      <c r="A15" s="35" t="inlineStr">
+      <c r="A15" s="34" t="inlineStr">
         <is>
           <t>Financing support</t>
         </is>
       </c>
-      <c r="B15" s="35" t="inlineStr">
+      <c r="B15" s="34" t="inlineStr">
         <is>
           <t>Support for the development of the energy market ecosystem.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="30.75" customHeight="1">
-      <c r="A16" s="35" t="inlineStr">
+      <c r="A16" s="34" t="inlineStr">
         <is>
           <t>Medium Enterprises</t>
         </is>
       </c>
-      <c r="B16" s="35" t="inlineStr">
+      <c r="B16" s="34" t="inlineStr">
         <is>
           <t>Support for the development of medium enterprises in the energy transition market.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="30.75" customHeight="1">
-      <c r="A17" s="35" t="inlineStr">
+      <c r="A17" s="34" t="inlineStr">
         <is>
           <t>Small Enterprises</t>
         </is>
       </c>
-      <c r="B17" s="35" t="inlineStr">
+      <c r="B17" s="34" t="inlineStr">
         <is>
           <t>Support for the development of small enterprises in the energy transition market.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="30.75" customHeight="1">
-      <c r="A18" s="35" t="inlineStr">
+      <c r="A18" s="34" t="inlineStr">
         <is>
           <t>Capacity Building Training</t>
         </is>
       </c>
-      <c r="B18" s="35" t="inlineStr">
+      <c r="B18" s="34" t="inlineStr">
         <is>
           <t>Number of people benefiting from training on energy business, energy finance, or related implementation capacity.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="76.5" customHeight="1">
-      <c r="A19" s="35" t="inlineStr">
+      <c r="A19" s="34" t="inlineStr">
         <is>
           <t>Entrepreneurship Training</t>
         </is>
       </c>
-      <c r="B19" s="35" t="inlineStr">
+      <c r="B19" s="34" t="inlineStr">
         <is>
           <t>Training for enterprises on the energy business, assumed to result in direct beneficiaries.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="30.75" customHeight="1">
-      <c r="A20" s="35" t="inlineStr">
+      <c r="A20" s="34" t="inlineStr">
         <is>
           <t>Market Intervention</t>
         </is>
       </c>
-      <c r="B20" s="35" t="inlineStr">
+      <c r="B20" s="34" t="inlineStr">
         <is>
           <t>Volume of investment leveraged or barriers removed for clean, reliable, affordable, and sustainable energy solutions.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="45.75" customHeight="1">
-      <c r="A21" s="35" t="inlineStr">
+      <c r="A21" s="34" t="inlineStr">
         <is>
           <t>Campaign Participant</t>
         </is>
       </c>
-      <c r="B21" s="35" t="inlineStr">
+      <c r="B21" s="34" t="inlineStr">
         <is>
           <t>Individuals who participate in advocacy or awareness campaigns on energy.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="30.75" customHeight="1">
-      <c r="A22" s="35" t="inlineStr">
+      <c r="A22" s="34" t="inlineStr">
         <is>
           <t>Policy or Regulatory Framework</t>
         </is>
       </c>
-      <c r="B22" s="35" t="inlineStr">
+      <c r="B22" s="34" t="inlineStr">
         <is>
           <t>Policies, regulations, strategies, plans, or frameworks developed, approved, implemented, or strengthened.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="35" t="inlineStr">
+      <c r="A23" s="34" t="inlineStr">
         <is>
           <t>GHG Emissions Reduction</t>
         </is>
       </c>
-      <c r="B23" s="35" t="inlineStr">
+      <c r="B23" s="34" t="inlineStr">
         <is>
           <t>Greenhouse gas emissions reduced or mitigated, in tCO2e.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="35" t="inlineStr">
+      <c r="A24" s="34" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="B24" s="35" t="inlineStr">
+      <c r="B24" s="34" t="inlineStr">
         <is>
           <t>Energy-related output that does not fit the standard categories above.</t>
         </is>
